--- a/data/samsun/Veriler.xlsx
+++ b/data/samsun/Veriler.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\samsun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7181F13E-7873-4A7E-8620-66C802830D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0B95B5-F723-4AD8-A2C3-0DB1B83EC179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="203">
   <si>
     <t>Traction_Converter</t>
   </si>
@@ -585,9 +585,6 @@
     <t>Arıza Tipi</t>
   </si>
   <si>
-    <t>MC</t>
-  </si>
-  <si>
     <t>A-Kritik/Emniyet Riski</t>
   </si>
   <si>
@@ -637,6 +634,15 @@
   </si>
   <si>
     <t>SAMSUN</t>
+  </si>
+  <si>
+    <t>MC1</t>
+  </si>
+  <si>
+    <t>MC2</t>
+  </si>
+  <si>
+    <t>SC</t>
   </si>
 </sst>
 </file>
@@ -2363,7 +2369,7 @@
         <v>182</v>
       </c>
       <c r="G1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2371,22 +2377,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" t="s">
         <v>183</v>
-      </c>
-      <c r="D2" t="s">
-        <v>184</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2394,19 +2400,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" t="s">
         <v>186</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>187</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="17" t="s">
         <v>188</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2414,16 +2420,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" t="s">
         <v>190</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>191</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="17" t="s">
         <v>192</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2431,10 +2437,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" t="s">
         <v>194</v>
-      </c>
-      <c r="D5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -2442,17 +2448,23 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
+      <c r="C7" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
